--- a/ru/downloads/data-excel/10.2.1.xlsx
+++ b/ru/downloads/data-excel/10.2.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11235" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -787,14 +787,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35.42578125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>23</v>
       </c>
@@ -805,7 +805,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
@@ -816,7 +816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -829,8 +829,9 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -867,8 +868,11 @@
       <c r="L4" s="7">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" s="4" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" s="14">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="4" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>25</v>
       </c>
@@ -905,8 +909,11 @@
       <c r="L5" s="15">
         <v>8140.625</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="15">
+        <v>9201.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>24</v>
       </c>
@@ -943,8 +950,11 @@
       <c r="L6" s="16">
         <v>10.846001303403501</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="16">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="3" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -961,7 +971,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
@@ -998,8 +1008,11 @@
       <c r="L8" s="15">
         <v>10.988094566305252</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" s="15">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
@@ -1036,8 +1049,11 @@
       <c r="L9" s="15">
         <v>10.763648271774647</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" s="15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>56</v>
       </c>
@@ -1054,7 +1070,7 @@
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
     </row>
-    <row r="11" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
@@ -1091,8 +1107,11 @@
       <c r="L11" s="15">
         <v>10.76698085224611</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" s="15">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>31</v>
       </c>
@@ -1129,8 +1148,11 @@
       <c r="L12" s="15">
         <v>10.932626856127836</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" s="15">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>58</v>
       </c>
@@ -1147,7 +1169,7 @@
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
     </row>
-    <row r="14" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>32</v>
       </c>
@@ -1184,8 +1206,11 @@
       <c r="L14" s="17">
         <v>10.106153564811303</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" s="17">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>33</v>
       </c>
@@ -1222,8 +1247,11 @@
       <c r="L15" s="17">
         <v>9.3905727242980745</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" s="17">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
@@ -1260,8 +1288,11 @@
       <c r="L16" s="17">
         <v>13.266689769062884</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" s="17">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
@@ -1298,8 +1329,11 @@
       <c r="L17" s="17">
         <v>30.78040360209485</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="17">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>36</v>
       </c>
@@ -1336,8 +1370,9 @@
       <c r="L18" s="17">
         <v>6.3815606692693185</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" s="17"/>
+    </row>
+    <row r="19" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
@@ -1374,8 +1409,11 @@
       <c r="L19" s="17">
         <v>18.650723038521615</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" s="17">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
@@ -1412,8 +1450,11 @@
       <c r="L20" s="17">
         <v>11.874861429631871</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="17">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
@@ -1450,8 +1491,11 @@
       <c r="L21" s="17">
         <v>8.4047369664913738</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" s="17">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
         <v>40</v>
       </c>
@@ -1488,8 +1532,11 @@
       <c r="L22" s="27">
         <v>13.717539810602702</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22" s="27">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>57</v>
       </c>
@@ -1505,8 +1552,11 @@
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" s="1">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>50</v>
       </c>
@@ -1543,8 +1593,11 @@
       <c r="L24" s="15">
         <v>15.058555587857562</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" s="15">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>51</v>
       </c>
@@ -1581,8 +1634,11 @@
       <c r="L25" s="15">
         <v>8.6422735249843061</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="M25" s="15">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>52</v>
       </c>
@@ -1619,8 +1675,11 @@
       <c r="L26" s="13">
         <v>9.3356487302577893</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="13">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="32" t="s">
         <v>53</v>
       </c>
@@ -1656,6 +1715,9 @@
       </c>
       <c r="L27" s="30">
         <v>4.1928103341023091</v>
+      </c>
+      <c r="M27" s="30">
+        <v>10.199999999999999</v>
       </c>
     </row>
   </sheetData>
